--- a/demo/crm/Azure_Government_FedRAMP_High_CRM.xlsx
+++ b/demo/crm/Azure_Government_FedRAMP_High_CRM.xlsx
@@ -901,17 +901,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Microsoft reviews Azure-internal audit logs continuously via the Microsoft security operations team and reports relevant findings to customers per IR-6.</t>
+          <t>Microsoft provides the log sources (Activity Log, Entra audit, Defender for Cloud, Sentinel) but performs no review of customer-tenant audit records on the customer's behalf.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for reviewing customer Activity Logs, Defender for Cloud alerts, Microsoft Sentinel incidents, and application logs on the customer-defined cadence (minimum weekly for non-critical, continuous for critical). Reportable findings escalated per IR-6.</t>
+          <t>Customer is solely responsible for reviewing, analyzing, and reporting on customer Activity Logs, Defender for Cloud alerts, Microsoft Sentinel incidents, and application logs on the customer-defined cadence (minimum weekly for non-critical, continuous for critical). The customer operates the Sentinel workspace and escalates reportable findings per IR-6.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1349,17 +1349,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Inherited</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Microsoft provides FIPS 140-2 validated cryptographic modules within Azure Government via Key Vault, Managed HSM, and FIPS-validated service endpoints.</t>
+          <t>Microsoft provides FIPS 140-2 validated cryptographic modules within Azure Government via Key Vault, Managed HSM, and FIPS-validated service endpoints; the customer workload consumes only these validated modules and implements no independent cryptography.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for using only FIPS 140-2 validated cryptographic implementations: enable FIPS-validated endpoints for customer service calls, configure FIPS mode in customer guest operating systems where supported, avoid non-FIPS algorithms in applications, and document customer cryptographic implementations in the SSP.</t>
+          <t>Customer fully inherits the FIPS 140-2 validated cryptographic modules provided by Azure Government. The customer SSP references the Azure Government FedRAMP High SSP as the authoritative source; no customer-side cryptographic implementation is required for this control.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">

--- a/demo/crm/Azure_Government_FedRAMP_High_CRM.xlsx
+++ b/demo/crm/Azure_Government_FedRAMP_High_CRM.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -475,12 +475,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PE-1</t>
+          <t>AC-17</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Physical and Environmental Protection Policy and Procedures</t>
+          <t>Remote Access</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -490,12 +490,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Microsoft develops, documents, and annually reviews physical and environmental protection policy and procedures for all Azure Government datacenter regions. Policy applies to all Microsoft-owned, -leased, and -colocated facilities supporting the Azure Government cloud.</t>
+          <t>Microsoft operates Azure Bastion as a fully-managed, hardened remote-access plane: browser-based RDP/SSH over TLS with no public IPs on customer VMs, patched and monitored by Microsoft.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Customer fully inherits the Microsoft physical and environmental protection policy for all customer workloads hosted in Azure Government. No customer action required for the underlying infrastructure layer. Customer SSP must reference the Azure Government FedRAMP High SSP (available via the Service Trust Portal) as the authoritative source.</t>
+          <t>Customer fully inherits the managed Azure Bastion remote-access control for administrative access to customer VMs. No customer-built VPN or jump-host is required; the customer SSP references the Azure Government FedRAMP High SSP as the authoritative source for the inherited remote-access plane.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -507,12 +507,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>PE-2</t>
+          <t>PE-1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Physical Access Authorizations</t>
+          <t>Physical and Environmental Protection Policy and Procedures</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Microsoft maintains and reviews the list of personnel authorized to access Azure datacenter facilities. Access is re-approved at least every 90 days and revoked within 24 hours of separation or role change.</t>
+          <t>Microsoft develops, documents, and annually reviews physical and environmental protection policy and procedures for all Azure Government datacenter regions. Policy applies to all Microsoft-owned, -leased, and -colocated facilities supporting the Azure Government cloud.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Customer fully inherits Azure physical access authorization controls. Customer personnel are not granted physical access to Azure Government datacenters. No customer-side implementation required.</t>
+          <t>Customer fully inherits the Microsoft physical and environmental protection policy for all customer workloads hosted in Azure Government. No customer action required for the underlying infrastructure layer. Customer SSP must reference the Azure Government FedRAMP High SSP (available via the Service Trust Portal) as the authoritative source.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -539,12 +539,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>PE-3</t>
+          <t>PE-2</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Physical Access Control</t>
+          <t>Physical Access Authorizations</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Microsoft enforces datacenter physical access via perimeter fencing, badge plus biometric authentication at building and cage boundaries, mantrap vestibules, 24x7 security staff, and full visitor escort. Access events are logged and retained per AU-11.</t>
+          <t>Microsoft maintains and reviews the list of personnel authorized to access Azure datacenter facilities. Access is re-approved at least every 90 days and revoked within 24 hours of separation or role change.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Customer fully inherits Microsoft datacenter physical access controls and has no compensating-control responsibility.</t>
+          <t>Customer fully inherits Azure physical access authorization controls. Customer personnel are not granted physical access to Azure Government datacenters. No customer-side implementation required.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -571,12 +571,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>PE-6</t>
+          <t>PE-3</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Monitoring Physical Access</t>
+          <t>Physical Access Control</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -586,12 +586,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Microsoft monitors datacenter physical access via CCTV with 90-day minimum retention, intrusion-detection sensors, and continuous review by the Microsoft datacenter security operations team with automated alerting on anomalous access.</t>
+          <t>Microsoft enforces datacenter physical access via perimeter fencing, badge plus biometric authentication at building and cage boundaries, mantrap vestibules, 24x7 security staff, and full visitor escort. Access events are logged and retained per AU-11.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Customer fully inherits Azure physical access monitoring. Customer may review the Azure SOC 2 Type II and FedRAMP High audit reports via the Service Trust Portal for assurance evidence.</t>
+          <t>Customer fully inherits Microsoft datacenter physical access controls and has no compensating-control responsibility.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -603,12 +603,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>PE-13</t>
+          <t>PE-6</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Fire Protection</t>
+          <t>Monitoring Physical Access</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -618,12 +618,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Azure datacenters deploy very-early smoke detection, pre-action dry-pipe suppression, handheld extinguishers per NFPA 10, and conduct quarterly inspection with annual recertification of suppression equipment.</t>
+          <t>Microsoft monitors datacenter physical access via CCTV with 90-day minimum retention, intrusion-detection sensors, and continuous review by the Microsoft datacenter security operations team with automated alerting on anomalous access.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Customer fully inherits Azure datacenter fire protection. Customer data is protected against facility-level events through customer-implemented availability-zone / geo-redundant replication per CP-9.</t>
+          <t>Customer fully inherits Azure physical access monitoring. Customer may review the Azure SOC 2 Type II and FedRAMP High audit reports via the Service Trust Portal for assurance evidence.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -635,12 +635,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>PE-14</t>
+          <t>PE-13</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Environmental Controls</t>
+          <t>Fire Protection</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -650,12 +650,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Microsoft maintains datacenter temperature and humidity within ASHRAE ranges via N+1 redundant cooling with continuous monitoring and automated failover.</t>
+          <t>Azure datacenters deploy very-early smoke detection, pre-action dry-pipe suppression, handheld extinguishers per NFPA 10, and conduct quarterly inspection with annual recertification of suppression equipment.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Customer fully inherits Azure datacenter environmental controls. No customer-side implementation responsibility.</t>
+          <t>Customer fully inherits Azure datacenter fire protection. Customer data is protected against facility-level events through customer-implemented availability-zone / geo-redundant replication per CP-9.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -667,27 +667,27 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>PE-4</t>
+          <t>PE-14</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Access Control for Transmission</t>
+          <t>Environmental Controls</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Inherited</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Microsoft controls physical access to all information system transmission and distribution lines within Azure datacenter facilities, including intra-facility fiber, copper, and power distribution.</t>
+          <t>Microsoft maintains datacenter temperature and humidity within ASHRAE ranges via N+1 redundant cooling with continuous monitoring and automated failover.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Provider-owned. Customer has no role in physical transmission-line access control within Azure datacenters and no compensating-control responsibility.</t>
+          <t>Customer fully inherits Azure datacenter environmental controls. No customer-side implementation responsibility.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -699,12 +699,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>PE-5</t>
+          <t>PE-4</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Access Control for Output Devices</t>
+          <t>Access Control for Transmission</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Microsoft controls physical access to output devices within Azure datacenter facilities. No physical output devices are provided to customers; all customer interaction occurs via authenticated remote APIs and the Azure portal.</t>
+          <t>Microsoft controls physical access to all information system transmission and distribution lines within Azure datacenter facilities, including intra-facility fiber, copper, and power distribution.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Provider-owned. Customer does not maintain physical output devices in Azure facilities. Not applicable to customer.</t>
+          <t>Provider-owned. Customer has no role in physical transmission-line access control within Azure datacenters and no compensating-control responsibility.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -731,27 +731,27 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AC-1</t>
+          <t>PE-5</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Access Control Policy and Procedures</t>
+          <t>Access Control for Output Devices</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Microsoft maintains internal access control policy for Microsoft personnel and Azure-managed infrastructure, reviewed annually.</t>
+          <t>Microsoft controls physical access to output devices within Azure datacenter facilities. No physical output devices are provided to customers; all customer interaction occurs via authenticated remote APIs and the Azure portal.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing, documenting, disseminating, and annually reviewing the customer-side access control policy governing customer use of Azure services and customer-deployed workloads. Customer SSP must document the AC-1 policy and its mission alignment.</t>
+          <t>Provider-owned. Customer does not maintain physical output devices in Azure facilities. Not applicable to customer.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -763,12 +763,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AC-2</t>
+          <t>AC-1</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Account Management</t>
+          <t>Access Control Policy and Procedures</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Microsoft manages Microsoft-internal personnel accounts per Microsoft Personnel Security policy and provides Microsoft Entra ID, Privileged Identity Management (PIM), and managed identities as account-management primitives for customer use.</t>
+          <t>Microsoft maintains internal access control policy for Microsoft personnel and Azure-managed infrastructure, reviewed annually.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for the full lifecycle of customer Entra ID users, groups, service principals, and managed identities, including (a) provisioning per documented request/approval workflow, (b) deprovisioning within 24 hours of role change or separation, (c) quarterly access reviews via Entra ID Access Reviews, (d) automated disabling of accounts inactive &gt;=90 days, and (e) MFA enforcement on all Global Administrator accounts.</t>
+          <t>Customer is responsible for developing, documenting, disseminating, and annually reviewing the customer-side access control policy governing customer use of Azure services and customer-deployed workloads. Customer SSP must document the AC-1 policy and its mission alignment.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -795,12 +795,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AC-3</t>
+          <t>AC-2</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Access Enforcement</t>
+          <t>Account Management</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -810,12 +810,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Microsoft enforces access at the Azure Resource Manager control-plane layer; requests not authorized by an applicable Azure RBAC role assignment or Azure Policy are denied.</t>
+          <t>Microsoft manages Microsoft-internal personnel accounts per Microsoft Personnel Security policy and provides Microsoft Entra ID, Privileged Identity Management (PIM), and managed identities as account-management primitives for customer use.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for authoring and maintaining Azure RBAC role assignments, custom roles, Azure Policy assignments, and Conditional Access policies that enforce least-privilege access to customer-owned resources, and for validating effective access prior to deployment.</t>
+          <t>Customer is responsible for the full lifecycle of customer Entra ID users, groups, service principals, and managed identities, including (a) provisioning per documented request/approval workflow, (b) deprovisioning within 24 hours of role change or separation, (c) quarterly access reviews via Entra ID Access Reviews, (d) automated disabling of accounts inactive &gt;=90 days, and (e) MFA enforcement on all Global Administrator accounts.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -827,12 +827,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AC-6</t>
+          <t>AC-3</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Least Privilege</t>
+          <t>Access Enforcement</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -842,12 +842,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Microsoft implements least privilege for Microsoft personnel and Azure service principals via narrowly scoped built-in roles.</t>
+          <t>Microsoft enforces access at the Azure Resource Manager control-plane layer; requests not authorized by an applicable Azure RBAC role assignment or Azure Policy are denied.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for implementing least privilege within customer subscriptions: (a) custom RBAC roles scoped to minimum actions, (b) just-in-time privileged elevation via Entra PIM, (c) periodic review and removal of unused role assignments, and (d) management-group-level Azure Policy to constrain delegated administration.</t>
+          <t>Customer is responsible for authoring and maintaining Azure RBAC role assignments, custom roles, Azure Policy assignments, and Conditional Access policies that enforce least-privilege access to customer-owned resources, and for validating effective access prior to deployment.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AU-2</t>
+          <t>AC-6</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Event Logging</t>
+          <t>Least Privilege</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Microsoft logs all control-plane operations via Azure-internal audit systems and provides Azure Activity Log, Azure Monitor, diagnostic settings, and Microsoft Entra audit logs for customer event capture.</t>
+          <t>Microsoft implements least privilege for Microsoft personnel and Azure service principals via narrowly scoped built-in roles.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for (a) routing Activity Log and resource diagnostic logs to a Log Analytics workspace and immutable storage, (b) enabling data-plane logging on sensitive storage accounts, Key Vaults, and databases, (c) configuring Entra ID sign-in and audit log export, and (d) documenting the customer-defined auditable event list per AU-1.</t>
+          <t>Customer is responsible for implementing least privilege within customer subscriptions: (a) custom RBAC roles scoped to minimum actions, (b) just-in-time privileged elevation via Entra PIM, (c) periodic review and removal of unused role assignments, and (d) management-group-level Azure Policy to constrain delegated administration.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -891,27 +891,27 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AU-6</t>
+          <t>AU-2</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Audit Record Review, Analysis, and Reporting</t>
+          <t>Event Logging</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Microsoft provides the log sources (Activity Log, Entra audit, Defender for Cloud, Sentinel) but performs no review of customer-tenant audit records on the customer's behalf.</t>
+          <t>Microsoft logs all control-plane operations via Azure-internal audit systems and provides Azure Activity Log, Azure Monitor, diagnostic settings, and Microsoft Entra audit logs for customer event capture.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Customer is solely responsible for reviewing, analyzing, and reporting on customer Activity Logs, Defender for Cloud alerts, Microsoft Sentinel incidents, and application logs on the customer-defined cadence (minimum weekly for non-critical, continuous for critical). The customer operates the Sentinel workspace and escalates reportable findings per IR-6.</t>
+          <t>Customer is responsible for (a) routing Activity Log and resource diagnostic logs to a Log Analytics workspace and immutable storage, (b) enabling data-plane logging on sensitive storage accounts, Key Vaults, and databases, (c) configuring Entra ID sign-in and audit log export, and (d) documenting the customer-defined auditable event list per AU-1.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -923,27 +923,27 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>AU-12</t>
+          <t>AU-6</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Audit Record Generation</t>
+          <t>Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Microsoft generates audit records for all Azure control-plane and Azure-internal service operations per Microsoft audit policy.</t>
+          <t>Microsoft provides the log sources (Activity Log, Entra audit, Defender for Cloud, Sentinel) but performs no review of customer-tenant audit records on the customer's behalf.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for enabling audit record generation on all customer-deployed systems: VM guest OS auditd / Windows Event Log via Azure Monitor Agent, Azure SQL audit, container runtime logs, and application logs, forwarded to a tamper-resistant Log Analytics workspace or immutable storage.</t>
+          <t>Customer is solely responsible for reviewing, analyzing, and reporting on customer Activity Logs, Defender for Cloud alerts, Microsoft Sentinel incidents, and application logs on the customer-defined cadence (minimum weekly for non-critical, continuous for critical). The customer operates the Sentinel workspace and escalates reportable findings per IR-6.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -955,12 +955,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>CM-2</t>
+          <t>AU-12</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Baseline Configuration</t>
+          <t>Audit Record Generation</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -970,12 +970,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Microsoft maintains baseline configurations for all Azure-managed infrastructure and services per Microsoft configuration management policy.</t>
+          <t>Microsoft generates audit records for all Azure control-plane and Azure-internal service operations per Microsoft audit policy.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing and maintaining baseline configurations for customer-managed VM images, container images, and Infrastructure-as-Code templates (ARM, Bicep, Terraform). Baselines reviewed at least annually and after significant change; drift detected via Azure Policy guest configuration / Machine Configuration.</t>
+          <t>Customer is responsible for enabling audit record generation on all customer-deployed systems: VM guest OS auditd / Windows Event Log via Azure Monitor Agent, Azure SQL audit, container runtime logs, and application logs, forwarded to a tamper-resistant Log Analytics workspace or immutable storage.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -987,12 +987,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CM-6</t>
+          <t>CM-2</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Configuration Settings</t>
+          <t>Baseline Configuration</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1002,12 +1002,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Microsoft configures Azure-managed services per Microsoft security baselines aligned to the Microsoft cloud security benchmark.</t>
+          <t>Microsoft maintains baseline configurations for all Azure-managed infrastructure and services per Microsoft configuration management policy.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for (a) hardening customer-managed OS images per DISA STIG or CIS Benchmarks, (b) continuously enforcing configuration via Azure Policy and Machine Configuration, (c) remediating drift within customer-defined SLAs, and (d) documenting approved deviations with compensating controls.</t>
+          <t>Customer is responsible for developing and maintaining baseline configurations for customer-managed VM images, container images, and Infrastructure-as-Code templates (ARM, Bicep, Terraform). Baselines reviewed at least annually and after significant change; drift detected via Azure Policy guest configuration / Machine Configuration.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1019,12 +1019,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>CM-8</t>
+          <t>CM-6</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>System Component Inventory</t>
+          <t>Configuration Settings</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Microsoft maintains a complete inventory of Azure-managed physical and virtual infrastructure supporting the Azure Government offering.</t>
+          <t>Microsoft configures Azure-managed services per Microsoft security baselines aligned to the Microsoft cloud security benchmark.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for maintaining an accurate inventory of customer-deployed resources via Azure Resource Graph, Azure Resource tags, and Defender for Cloud asset inventory, reconciled at least monthly.</t>
+          <t>Customer is responsible for (a) hardening customer-managed OS images per DISA STIG or CIS Benchmarks, (b) continuously enforcing configuration via Azure Policy and Machine Configuration, (c) remediating drift within customer-defined SLAs, and (d) documenting approved deviations with compensating controls.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1051,12 +1051,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>CP-9</t>
+          <t>CM-8</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>System Backup</t>
+          <t>System Component Inventory</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Microsoft replicates and backs up Azure-managed control-plane and service data per Microsoft contingency planning policy, with locally and geo-redundant storage durability guarantees.</t>
+          <t>Microsoft maintains a complete inventory of Azure-managed physical and virtual infrastructure supporting the Azure Government offering.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for backing up customer-owned data aligned to customer-defined RPO via Azure Backup vaults, VM and disk snapshots, Azure SQL automated backups with geo-restore, and geo-redundant storage replication. Backup integrity tested per CP-4.</t>
+          <t>Customer is responsible for maintaining an accurate inventory of customer-deployed resources via Azure Resource Graph, Azure Resource tags, and Defender for Cloud asset inventory, reconciled at least monthly.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>IA-2</t>
+          <t>CP-9</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Identification and Authentication (Organizational Users)</t>
+          <t>System Backup</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Microsoft authenticates Microsoft personnel via internal MFA and PIV-equivalent credentials and provides Microsoft Entra ID with Conditional Access and FIDO2 / certificate-based authentication for customer use.</t>
+          <t>Microsoft replicates and backs up Azure-managed control-plane and service data per Microsoft contingency planning policy, with locally and geo-redundant storage durability guarantees.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for (a) enforcing MFA on all customer Entra ID users via Conditional Access, with phishing-resistant MFA for privileged roles, (b) federating with the customer enterprise IdP where applicable, (c) enforcing FIPS 140-validated authenticators for government-user access, and (d) blocking legacy authentication protocols.</t>
+          <t>Customer is responsible for backing up customer-owned data aligned to customer-defined RPO via Azure Backup vaults, VM and disk snapshots, Azure SQL automated backups with geo-restore, and geo-redundant storage replication. Backup integrity tested per CP-4.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1115,12 +1115,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>IA-5</t>
+          <t>IA-2</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Authenticator Management</t>
+          <t>Identification and Authentication (Organizational Users)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Microsoft manages authenticators for Microsoft personnel per Microsoft Personnel Security policy including issuance, rotation, and revocation.</t>
+          <t>Microsoft authenticates Microsoft personnel via internal MFA and PIV-equivalent credentials and provides Microsoft Entra ID with Conditional Access and FIDO2 / certificate-based authentication for customer use.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for managing customer-side authenticators: (a) Entra ID password protection and ban-list policy, (b) service-principal secret and certificate rotation, (c) MFA device lifecycle including loss reporting and re-issuance, and (d) Azure Key Vault rotation policies for application secrets and certificates.</t>
+          <t>Customer is responsible for (a) enforcing MFA on all customer Entra ID users via Conditional Access, with phishing-resistant MFA for privileged roles, (b) federating with the customer enterprise IdP where applicable, (c) enforcing FIPS 140-validated authenticators for government-user access, and (d) blocking legacy authentication protocols.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1147,12 +1147,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>IR-4</t>
+          <t>IA-5</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Incident Handling</t>
+          <t>Authenticator Management</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Microsoft handles incidents affecting Azure-managed infrastructure per the Microsoft Security Response process and notifies affected customers per the Microsoft Online Services Terms.</t>
+          <t>Microsoft manages authenticators for Microsoft personnel per Microsoft Personnel Security policy including issuance, rotation, and revocation.</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for incident handling within the customer environment: detection via Defender for Cloud and Microsoft Sentinel, triage per customer playbooks, containment via Conditional Access revocation and NSG isolation, eradication and recovery per the customer IR plan, and breach notification per regulatory obligations.</t>
+          <t>Customer is responsible for managing customer-side authenticators: (a) Entra ID password protection and ban-list policy, (b) service-principal secret and certificate rotation, (c) MFA device lifecycle including loss reporting and re-issuance, and (d) Azure Key Vault rotation policies for application secrets and certificates.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1179,12 +1179,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>IR-6</t>
+          <t>IR-4</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Incident Reporting</t>
+          <t>Incident Handling</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Microsoft reports incidents affecting Azure-managed infrastructure to affected customers and to the FedRAMP PMO per Microsoft incident reporting procedures.</t>
+          <t>Microsoft handles incidents affecting Azure-managed infrastructure per the Microsoft Security Response process and notifies affected customers per the Microsoft Online Services Terms.</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for reporting customer-environment incidents to customer authorities, to US-CERT per FISMA timeframes, and to the FedRAMP PMO within 1 hour of incident determination for FedRAMP-authorized systems.</t>
+          <t>Customer is responsible for incident handling within the customer environment: detection via Defender for Cloud and Microsoft Sentinel, triage per customer playbooks, containment via Conditional Access revocation and NSG isolation, eradication and recovery per the customer IR plan, and breach notification per regulatory obligations.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1211,12 +1211,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>MA-4</t>
+          <t>IR-6</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Nonlocal Maintenance</t>
+          <t>Incident Reporting</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Microsoft authorizes, monitors, and audits all nonlocal maintenance on Azure-managed infrastructure via approved internal access paths with MFA and full session recording.</t>
+          <t>Microsoft reports incidents affecting Azure-managed infrastructure to affected customers and to the FedRAMP PMO per Microsoft incident reporting procedures.</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for nonlocal maintenance of customer-managed resources: administrative access via Azure Bastion (no direct public SSH/RDP), MFA on all administrative sessions, session logging to immutable storage, and FIPS-validated transport for administrative connections.</t>
+          <t>Customer is responsible for reporting customer-environment incidents to customer authorities, to US-CERT per FISMA timeframes, and to the FedRAMP PMO within 1 hour of incident determination for FedRAMP-authorized systems.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1243,12 +1243,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>SC-7</t>
+          <t>MA-4</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Boundary Protection</t>
+          <t>Nonlocal Maintenance</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Microsoft provides Virtual Network, Network Security Groups, Azure Firewall, DDoS Protection, Application Gateway WAF, and Private Link as boundary-protection primitives, and protects the Azure service boundary at the control-plane layer.</t>
+          <t>Microsoft authorizes, monitors, and audits all nonlocal maintenance on Azure-managed infrastructure via approved internal access paths with MFA and full session recording.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for designing the customer virtual-network boundary: (a) subnet segmentation, (b) NSG rules enforcing least-privilege flows, (c) Azure Firewall for centralized egress filtering, (d) WAF on internet-facing Application Gateways and Front Door, (e) Private Endpoints for PaaS services, and (f) enforcement of the customer-defined trust-zone boundary.</t>
+          <t>Customer is responsible for nonlocal maintenance of customer-managed resources: administrative access via Azure Bastion (no direct public SSH/RDP), MFA on all administrative sessions, session logging to immutable storage, and FIPS-validated transport for administrative connections.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1275,12 +1275,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>SC-8</t>
+          <t>SC-7</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Transmission Confidentiality and Integrity</t>
+          <t>Boundary Protection</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Microsoft encrypts data in transit between Azure services and across regions using TLS 1.2+ with FIPS-validated cipher suites and physically protects inter-datacenter fiber.</t>
+          <t>Microsoft provides Virtual Network, Network Security Groups, Azure Firewall, DDoS Protection, Application Gateway WAF, and Private Link as boundary-protection primitives, and protects the Azure service boundary at the control-plane layer.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for (a) enforcing TLS 1.2+ on all customer-facing endpoints, (b) configuring only approved FIPS-validated cipher suites, (c) enforcing HTTPS-only access, (d) application-layer TLS for service-to-service traffic, and (e) using Azure Government FIPS endpoints for FISMA-regulated systems.</t>
+          <t>Customer is responsible for designing the customer virtual-network boundary: (a) subnet segmentation, (b) NSG rules enforcing least-privilege flows, (c) Azure Firewall for centralized egress filtering, (d) WAF on internet-facing Application Gateways and Front Door, (e) Private Endpoints for PaaS services, and (f) enforcement of the customer-defined trust-zone boundary.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1307,12 +1307,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>SC-12</t>
+          <t>SC-8</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Cryptographic Key Establishment and Management</t>
+          <t>Transmission Confidentiality and Integrity</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Microsoft manages keys for Microsoft-managed encryption and provides Azure Key Vault (FIPS 140-2 Level 2 validated HSMs) and Azure Key Vault Managed HSM (FIPS 140-2 Level 3) for customer key management.</t>
+          <t>Microsoft encrypts data in transit between Azure services and across regions using TLS 1.2+ with FIPS-validated cipher suites and physically protects inter-datacenter fiber.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for managing customer-managed keys: (a) creation with appropriate key type and size, (b) rotation policy enabled, (c) Key Vault access policies / RBAC enforcing least privilege, (d) diagnostic logging of all key operations, and (e) soft-delete and purge protection prior to permanent removal.</t>
+          <t>Customer is responsible for (a) enforcing TLS 1.2+ on all customer-facing endpoints, (b) configuring only approved FIPS-validated cipher suites, (c) enforcing HTTPS-only access, (d) application-layer TLS for service-to-service traffic, and (e) using Azure Government FIPS endpoints for FISMA-regulated systems.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1339,27 +1339,27 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>SC-13</t>
+          <t>SC-12</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Cryptographic Protection</t>
+          <t>Cryptographic Key Establishment and Management</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Inherited</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Microsoft provides FIPS 140-2 validated cryptographic modules within Azure Government via Key Vault, Managed HSM, and FIPS-validated service endpoints; the customer workload consumes only these validated modules and implements no independent cryptography.</t>
+          <t>Microsoft manages keys for Microsoft-managed encryption and provides Azure Key Vault (FIPS 140-2 Level 2 validated HSMs) and Azure Key Vault Managed HSM (FIPS 140-2 Level 3) for customer key management.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Customer fully inherits the FIPS 140-2 validated cryptographic modules provided by Azure Government. The customer SSP references the Azure Government FedRAMP High SSP as the authoritative source; no customer-side cryptographic implementation is required for this control.</t>
+          <t>Customer is responsible for managing customer-managed keys: (a) creation with appropriate key type and size, (b) rotation policy enabled, (c) Key Vault access policies / RBAC enforcing least privilege, (d) diagnostic logging of all key operations, and (e) soft-delete and purge protection prior to permanent removal.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1371,27 +1371,27 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>SI-2</t>
+          <t>SC-13</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Flaw Remediation</t>
+          <t>Cryptographic Protection</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Inherited</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Microsoft identifies and remediates flaws in Azure-managed services per the Microsoft Vulnerability Management program and publishes service security advisories.</t>
+          <t>Microsoft provides FIPS 140-2 validated cryptographic modules within Azure Government via Key Vault, Managed HSM, and FIPS-validated service endpoints; the customer workload consumes only these validated modules and implements no independent cryptography.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for remediating flaws in customer-managed components: (a) guest OS and application patching via Azure Update Manager, (b) Defender for Cloud recommendations remediation per SLA, (c) Critical CVEs within 30 days and High within 90 days of disclosure, (d) CISA Known Exploited Vulnerabilities entries within the BOD 22-01 mandated window, and (e) a documented exception process.</t>
+          <t>Customer fully inherits the FIPS 140-2 validated cryptographic modules provided by Azure Government. The customer SSP references the Azure Government FedRAMP High SSP as the authoritative source; no customer-side cryptographic implementation is required for this control.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1403,12 +1403,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>SI-3</t>
+          <t>SI-2</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Malicious Code Protection</t>
+          <t>Flaw Remediation</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Microsoft protects Azure-managed infrastructure against malicious code via internal endpoint protection and continuous SOC monitoring.</t>
+          <t>Microsoft identifies and remediates flaws in Azure-managed services per the Microsoft Vulnerability Management program and publishes service security advisories.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for deploying malicious code protection on customer workloads: Microsoft Defender for Servers or vendor EDR on VMs, Defender for Containers on AKS, signature/engine updates within 24 hours of release, and remediation of detections per IR-4.</t>
+          <t>Customer is responsible for remediating flaws in customer-managed components: (a) guest OS and application patching via Azure Update Manager, (b) Defender for Cloud recommendations remediation per SLA, (c) Critical CVEs within 30 days and High within 90 days of disclosure, (d) CISA Known Exploited Vulnerabilities entries within the BOD 22-01 mandated window, and (e) a documented exception process.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>SI-4</t>
+          <t>SI-3</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>System Monitoring</t>
+          <t>Malicious Code Protection</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Microsoft monitors Azure-managed infrastructure via internal SOC tooling with 24x7 coverage and automated alerting.</t>
+          <t>Microsoft protects Azure-managed infrastructure against malicious code via internal endpoint protection and continuous SOC monitoring.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for monitoring customer-deployed workloads via (a) Azure Monitor metrics and alerts, (b) Microsoft Defender for Cloud across all subscriptions, (c) Microsoft Sentinel for SIEM/SOAR correlation, (d) Defender for Cloud vulnerability assessment, and (e) customer SIEM integration where applicable. Alerts triaged per IR-4.</t>
+          <t>Customer is responsible for deploying malicious code protection on customer workloads: Microsoft Defender for Servers or vendor EDR on VMs, Defender for Containers on AKS, signature/engine updates within 24 hours of release, and remediation of detections per IR-4.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>MP-6</t>
+          <t>SI-4</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Media Sanitization</t>
+          <t>System Monitoring</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Microsoft sanitizes decommissioned physical storage media per NIST SP 800-88 Rev. 1 with documented certificates of destruction.</t>
+          <t>Microsoft monitors Azure-managed infrastructure via internal SOC tooling with 24x7 coverage and automated alerting.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for sanitizing customer-managed data: disk deletion (customer-managed key deletion = cryptographic erasure), purging versioned storage including soft-deleted blobs, database deletion, and scheduled purge of customer-managed Key Vault keys that encrypted retired data.</t>
+          <t>Customer is responsible for monitoring customer-deployed workloads via (a) Azure Monitor metrics and alerts, (b) Microsoft Defender for Cloud across all subscriptions, (c) Microsoft Sentinel for SIEM/SOAR correlation, (d) Defender for Cloud vulnerability assessment, and (e) customer SIEM integration where applicable. Alerts triaged per IR-4.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1499,27 +1499,27 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>AT-1</t>
+          <t>MP-6</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Awareness and Training Policy and Procedures</t>
+          <t>Media Sanitization</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the Azure service boundary. Customer maintains the awareness and training policy independently.</t>
+          <t>Microsoft sanitizes decommissioned physical storage media per NIST SP 800-88 Rev. 1 with documented certificates of destruction.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing, documenting, disseminating, and annually reviewing the customer security awareness and training policy applicable to all personnel with access to customer information systems.</t>
+          <t>Customer is responsible for sanitizing customer-managed data: disk deletion (customer-managed key deletion = cryptographic erasure), purging versioned storage including soft-deleted blobs, database deletion, and scheduled purge of customer-managed Key Vault keys that encrypted retired data.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1531,12 +1531,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>AT-2</t>
+          <t>AT-1</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Literacy Training and Awareness</t>
+          <t>Awareness and Training Policy and Procedures</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the Azure service boundary.</t>
+          <t>Not applicable to the Azure service boundary. Customer maintains the awareness and training policy independently.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for providing security literacy training and awareness to all customer information system users on initial access, annually thereafter, and following significant environmental change, including role-based content.</t>
+          <t>Customer is responsible for developing, documenting, disseminating, and annually reviewing the customer security awareness and training policy applicable to all personnel with access to customer information systems.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>AT-3</t>
+          <t>AT-2</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Role-Based Training</t>
+          <t>Literacy Training and Awareness</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for providing role-based security training to personnel with significant security responsibilities (cloud administrators, security engineers, developers with production access) prior to access authorization and annually thereafter.</t>
+          <t>Customer is responsible for providing security literacy training and awareness to all customer information system users on initial access, annually thereafter, and following significant environmental change, including role-based content.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>PL-2</t>
+          <t>AT-3</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>System Security and Privacy Plans</t>
+          <t>Role-Based Training</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the Azure service boundary. Customer maintains the System Security Plan independently.</t>
+          <t>Not applicable to the Azure service boundary.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing and maintaining the customer System Security Plan covering customer-deployed workloads, customer responsibilities, and the explicit inheritance and shared responsibility relationships with Microsoft per this CRM.</t>
+          <t>Customer is responsible for providing role-based security training to personnel with significant security responsibilities (cloud administrators, security engineers, developers with production access) prior to access authorization and annually thereafter.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -1627,12 +1627,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>PM-9</t>
+          <t>PL-2</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Risk Management Strategy</t>
+          <t>System Security and Privacy Plans</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1642,12 +1642,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the Azure service boundary.</t>
+          <t>Not applicable to the Azure service boundary. Customer maintains the System Security Plan independently.</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing and implementing the customer Risk Management Strategy, including risk tolerance for customer-managed workloads in Azure Government and risk framing for the inherited and shared portions of the shared responsibility model.</t>
+          <t>Customer is responsible for developing and maintaining the customer System Security Plan covering customer-deployed workloads, customer responsibilities, and the explicit inheritance and shared responsibility relationships with Microsoft per this CRM.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>RA-3</t>
+          <t>PM-9</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Risk Assessment</t>
+          <t>Risk Management Strategy</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for conducting risk assessments of customer-deployed systems at least annually and following significant change, incorporating the Azure shared responsibility model and the customer-specific threat landscape.</t>
+          <t>Customer is responsible for developing and implementing the customer Risk Management Strategy, including risk tolerance for customer-managed workloads in Azure Government and risk framing for the inherited and shared portions of the shared responsibility model.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>RA-5</t>
+          <t>RA-3</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Vulnerability Monitoring and Scanning</t>
+          <t>Risk Assessment</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the Azure service boundary. Microsoft scans Azure-managed infrastructure independently.</t>
+          <t>Not applicable to the Azure service boundary.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for vulnerability scanning of customer-deployed workloads via Microsoft Defender for Cloud vulnerability assessment, customer third-party scanners (Tenable Nessus, Qualys), and remediating findings per customer SLAs aligned to SI-2.</t>
+          <t>Customer is responsible for conducting risk assessments of customer-deployed systems at least annually and following significant change, incorporating the Azure shared responsibility model and the customer-specific threat landscape.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -1723,62 +1723,94 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>PE-10</t>
+          <t>RA-5</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Emergency Shutoff</t>
+          <t>Vulnerability Monitoring and Scanning</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the Azure Government customer service offering. Datacenter emergency power shutoff is a Microsoft-internal facility control not exposed to customer interaction.</t>
+          <t>Not applicable to the Azure service boundary. Microsoft scans Azure-managed infrastructure independently.</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to customer. Customer has no role in datacenter emergency shutoff procedures and no requirement to implement an equivalent compensating control.</t>
+          <t>Customer is responsible for vulnerability scanning of customer-deployed workloads via Microsoft Defender for Cloud vulnerability assessment, customer third-party scanners (Tenable Nessus, Qualys), and remediating findings per customer SLAs aligned to SI-2.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Not Implemented</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>PE-10</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Emergency Shutoff</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable to the Azure Government customer service offering. Datacenter emergency power shutoff is a Microsoft-internal facility control not exposed to customer interaction.</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable to customer. Customer has no role in datacenter emergency shutoff procedures and no requirement to implement an equivalent compensating control.</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Not Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
           <t>PE-11</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Emergency Power</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Not applicable to the Azure Government customer service offering. Microsoft provides datacenter emergency power (UPS, generators, fuel reserves) as an internal infrastructure control.</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Not applicable to customer. Azure datacenter emergency power is fully internal to Microsoft facilities; customer has no implementation or compensating-control responsibility.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Not Implemented</t>
         </is>

--- a/demo/crm/Azure_Government_FedRAMP_High_CRM.xlsx
+++ b/demo/crm/Azure_Government_FedRAMP_High_CRM.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -955,27 +955,27 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>AU-12</t>
+          <t>AU-9</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Audit Record Generation</t>
+          <t>Protection of Audit Information</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Microsoft generates audit records for all Azure control-plane and Azure-internal service operations per Microsoft audit policy.</t>
+          <t>Microsoft provides immutable storage primitives (Azure Blob immutable time-based retention / legal hold, Key Vault, Azure RBAC) but does not configure them on customer storage accounts.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for enabling audit record generation on all customer-deployed systems: VM guest OS auditd / Windows Event Log via Azure Monitor Agent, Azure SQL audit, container runtime logs, and application logs, forwarded to a tamper-resistant Log Analytics workspace or immutable storage.</t>
+          <t>Customer is responsible for protecting customer audit information: enabling immutable (WORM) time-based retention on the audit-log storage account, restricting access via least-privilege Azure RBAC, and enabling customer-managed-key encryption so audit records cannot be modified or deleted.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -987,12 +987,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CM-2</t>
+          <t>AU-12</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Baseline Configuration</t>
+          <t>Audit Record Generation</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1002,12 +1002,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Microsoft maintains baseline configurations for all Azure-managed infrastructure and services per Microsoft configuration management policy.</t>
+          <t>Microsoft generates audit records for all Azure control-plane and Azure-internal service operations per Microsoft audit policy.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing and maintaining baseline configurations for customer-managed VM images, container images, and Infrastructure-as-Code templates (ARM, Bicep, Terraform). Baselines reviewed at least annually and after significant change; drift detected via Azure Policy guest configuration / Machine Configuration.</t>
+          <t>Customer is responsible for enabling audit record generation on all customer-deployed systems: VM guest OS auditd / Windows Event Log via Azure Monitor Agent, Azure SQL audit, container runtime logs, and application logs, forwarded to a tamper-resistant Log Analytics workspace or immutable storage.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1019,12 +1019,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>CM-6</t>
+          <t>CM-2</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Configuration Settings</t>
+          <t>Baseline Configuration</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Microsoft configures Azure-managed services per Microsoft security baselines aligned to the Microsoft cloud security benchmark.</t>
+          <t>Microsoft maintains baseline configurations for all Azure-managed infrastructure and services per Microsoft configuration management policy.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for (a) hardening customer-managed OS images per DISA STIG or CIS Benchmarks, (b) continuously enforcing configuration via Azure Policy and Machine Configuration, (c) remediating drift within customer-defined SLAs, and (d) documenting approved deviations with compensating controls.</t>
+          <t>Customer is responsible for developing and maintaining baseline configurations for customer-managed VM images, container images, and Infrastructure-as-Code templates (ARM, Bicep, Terraform). Baselines reviewed at least annually and after significant change; drift detected via Azure Policy guest configuration / Machine Configuration.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1051,12 +1051,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>CM-8</t>
+          <t>CM-6</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>System Component Inventory</t>
+          <t>Configuration Settings</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Microsoft maintains a complete inventory of Azure-managed physical and virtual infrastructure supporting the Azure Government offering.</t>
+          <t>Microsoft configures Azure-managed services per Microsoft security baselines aligned to the Microsoft cloud security benchmark.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for maintaining an accurate inventory of customer-deployed resources via Azure Resource Graph, Azure Resource tags, and Defender for Cloud asset inventory, reconciled at least monthly.</t>
+          <t>Customer is responsible for (a) hardening customer-managed OS images per DISA STIG or CIS Benchmarks, (b) continuously enforcing configuration via Azure Policy and Machine Configuration, (c) remediating drift within customer-defined SLAs, and (d) documenting approved deviations with compensating controls.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>CP-9</t>
+          <t>CM-8</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>System Backup</t>
+          <t>System Component Inventory</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Microsoft replicates and backs up Azure-managed control-plane and service data per Microsoft contingency planning policy, with locally and geo-redundant storage durability guarantees.</t>
+          <t>Microsoft maintains a complete inventory of Azure-managed physical and virtual infrastructure supporting the Azure Government offering.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for backing up customer-owned data aligned to customer-defined RPO via Azure Backup vaults, VM and disk snapshots, Azure SQL automated backups with geo-restore, and geo-redundant storage replication. Backup integrity tested per CP-4.</t>
+          <t>Customer is responsible for maintaining an accurate inventory of customer-deployed resources via Azure Resource Graph, Azure Resource tags, and Defender for Cloud asset inventory, reconciled at least monthly.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1115,12 +1115,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>IA-2</t>
+          <t>CP-9</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Identification and Authentication (Organizational Users)</t>
+          <t>System Backup</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Microsoft authenticates Microsoft personnel via internal MFA and PIV-equivalent credentials and provides Microsoft Entra ID with Conditional Access and FIDO2 / certificate-based authentication for customer use.</t>
+          <t>Microsoft replicates and backs up Azure-managed control-plane and service data per Microsoft contingency planning policy, with locally and geo-redundant storage durability guarantees.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for (a) enforcing MFA on all customer Entra ID users via Conditional Access, with phishing-resistant MFA for privileged roles, (b) federating with the customer enterprise IdP where applicable, (c) enforcing FIPS 140-validated authenticators for government-user access, and (d) blocking legacy authentication protocols.</t>
+          <t>Customer is responsible for backing up customer-owned data aligned to customer-defined RPO via Azure Backup vaults, VM and disk snapshots, Azure SQL automated backups with geo-restore, and geo-redundant storage replication. Backup integrity tested per CP-4.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1147,12 +1147,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>IA-5</t>
+          <t>IA-2</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Authenticator Management</t>
+          <t>Identification and Authentication (Organizational Users)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Microsoft manages authenticators for Microsoft personnel per Microsoft Personnel Security policy including issuance, rotation, and revocation.</t>
+          <t>Microsoft authenticates Microsoft personnel via internal MFA and PIV-equivalent credentials and provides Microsoft Entra ID with Conditional Access and FIDO2 / certificate-based authentication for customer use.</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for managing customer-side authenticators: (a) Entra ID password protection and ban-list policy, (b) service-principal secret and certificate rotation, (c) MFA device lifecycle including loss reporting and re-issuance, and (d) Azure Key Vault rotation policies for application secrets and certificates.</t>
+          <t>Customer is responsible for (a) enforcing MFA on all customer Entra ID users via Conditional Access, with phishing-resistant MFA for privileged roles, (b) federating with the customer enterprise IdP where applicable, (c) enforcing FIPS 140-validated authenticators for government-user access, and (d) blocking legacy authentication protocols.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1179,12 +1179,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>IR-4</t>
+          <t>IA-5</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Incident Handling</t>
+          <t>Authenticator Management</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Microsoft handles incidents affecting Azure-managed infrastructure per the Microsoft Security Response process and notifies affected customers per the Microsoft Online Services Terms.</t>
+          <t>Microsoft manages authenticators for Microsoft personnel per Microsoft Personnel Security policy including issuance, rotation, and revocation.</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for incident handling within the customer environment: detection via Defender for Cloud and Microsoft Sentinel, triage per customer playbooks, containment via Conditional Access revocation and NSG isolation, eradication and recovery per the customer IR plan, and breach notification per regulatory obligations.</t>
+          <t>Customer is responsible for managing customer-side authenticators: (a) Entra ID password protection and ban-list policy, (b) service-principal secret and certificate rotation, (c) MFA device lifecycle including loss reporting and re-issuance, and (d) Azure Key Vault rotation policies for application secrets and certificates.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1211,12 +1211,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>IR-6</t>
+          <t>IR-4</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Incident Reporting</t>
+          <t>Incident Handling</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Microsoft reports incidents affecting Azure-managed infrastructure to affected customers and to the FedRAMP PMO per Microsoft incident reporting procedures.</t>
+          <t>Microsoft handles incidents affecting Azure-managed infrastructure per the Microsoft Security Response process and notifies affected customers per the Microsoft Online Services Terms.</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for reporting customer-environment incidents to customer authorities, to US-CERT per FISMA timeframes, and to the FedRAMP PMO within 1 hour of incident determination for FedRAMP-authorized systems.</t>
+          <t>Customer is responsible for incident handling within the customer environment: detection via Defender for Cloud and Microsoft Sentinel, triage per customer playbooks, containment via Conditional Access revocation and NSG isolation, eradication and recovery per the customer IR plan, and breach notification per regulatory obligations.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1243,12 +1243,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>MA-4</t>
+          <t>IR-6</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Nonlocal Maintenance</t>
+          <t>Incident Reporting</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Microsoft authorizes, monitors, and audits all nonlocal maintenance on Azure-managed infrastructure via approved internal access paths with MFA and full session recording.</t>
+          <t>Microsoft reports incidents affecting Azure-managed infrastructure to affected customers and to the FedRAMP PMO per Microsoft incident reporting procedures.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for nonlocal maintenance of customer-managed resources: administrative access via Azure Bastion (no direct public SSH/RDP), MFA on all administrative sessions, session logging to immutable storage, and FIPS-validated transport for administrative connections.</t>
+          <t>Customer is responsible for reporting customer-environment incidents to customer authorities, to US-CERT per FISMA timeframes, and to the FedRAMP PMO within 1 hour of incident determination for FedRAMP-authorized systems.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1275,12 +1275,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>SC-7</t>
+          <t>MA-4</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Boundary Protection</t>
+          <t>Nonlocal Maintenance</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Microsoft provides Virtual Network, Network Security Groups, Azure Firewall, DDoS Protection, Application Gateway WAF, and Private Link as boundary-protection primitives, and protects the Azure service boundary at the control-plane layer.</t>
+          <t>Microsoft authorizes, monitors, and audits all nonlocal maintenance on Azure-managed infrastructure via approved internal access paths with MFA and full session recording.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for designing the customer virtual-network boundary: (a) subnet segmentation, (b) NSG rules enforcing least-privilege flows, (c) Azure Firewall for centralized egress filtering, (d) WAF on internet-facing Application Gateways and Front Door, (e) Private Endpoints for PaaS services, and (f) enforcement of the customer-defined trust-zone boundary.</t>
+          <t>Customer is responsible for nonlocal maintenance of customer-managed resources: administrative access via Azure Bastion (no direct public SSH/RDP), MFA on all administrative sessions, session logging to immutable storage, and FIPS-validated transport for administrative connections.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1307,12 +1307,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>SC-8</t>
+          <t>SC-7</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Transmission Confidentiality and Integrity</t>
+          <t>Boundary Protection</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Microsoft encrypts data in transit between Azure services and across regions using TLS 1.2+ with FIPS-validated cipher suites and physically protects inter-datacenter fiber.</t>
+          <t>Microsoft provides Virtual Network, Network Security Groups, Azure Firewall, DDoS Protection, Application Gateway WAF, and Private Link as boundary-protection primitives, and protects the Azure service boundary at the control-plane layer.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for (a) enforcing TLS 1.2+ on all customer-facing endpoints, (b) configuring only approved FIPS-validated cipher suites, (c) enforcing HTTPS-only access, (d) application-layer TLS for service-to-service traffic, and (e) using Azure Government FIPS endpoints for FISMA-regulated systems.</t>
+          <t>Customer is responsible for designing the customer virtual-network boundary: (a) subnet segmentation, (b) NSG rules enforcing least-privilege flows, (c) Azure Firewall for centralized egress filtering, (d) WAF on internet-facing Application Gateways and Front Door, (e) Private Endpoints for PaaS services, and (f) enforcement of the customer-defined trust-zone boundary.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1339,12 +1339,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>SC-12</t>
+          <t>SC-8</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Cryptographic Key Establishment and Management</t>
+          <t>Transmission Confidentiality and Integrity</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Microsoft manages keys for Microsoft-managed encryption and provides Azure Key Vault (FIPS 140-2 Level 2 validated HSMs) and Azure Key Vault Managed HSM (FIPS 140-2 Level 3) for customer key management.</t>
+          <t>Microsoft encrypts data in transit between Azure services and across regions using TLS 1.2+ with FIPS-validated cipher suites and physically protects inter-datacenter fiber.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for managing customer-managed keys: (a) creation with appropriate key type and size, (b) rotation policy enabled, (c) Key Vault access policies / RBAC enforcing least privilege, (d) diagnostic logging of all key operations, and (e) soft-delete and purge protection prior to permanent removal.</t>
+          <t>Customer is responsible for (a) enforcing TLS 1.2+ on all customer-facing endpoints, (b) configuring only approved FIPS-validated cipher suites, (c) enforcing HTTPS-only access, (d) application-layer TLS for service-to-service traffic, and (e) using Azure Government FIPS endpoints for FISMA-regulated systems.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1371,27 +1371,27 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>SC-13</t>
+          <t>SC-12</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Cryptographic Protection</t>
+          <t>Cryptographic Key Establishment and Management</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Inherited</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Microsoft provides FIPS 140-2 validated cryptographic modules within Azure Government via Key Vault, Managed HSM, and FIPS-validated service endpoints; the customer workload consumes only these validated modules and implements no independent cryptography.</t>
+          <t>Microsoft manages keys for Microsoft-managed encryption and provides Azure Key Vault (FIPS 140-2 Level 2 validated HSMs) and Azure Key Vault Managed HSM (FIPS 140-2 Level 3) for customer key management.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Customer fully inherits the FIPS 140-2 validated cryptographic modules provided by Azure Government. The customer SSP references the Azure Government FedRAMP High SSP as the authoritative source; no customer-side cryptographic implementation is required for this control.</t>
+          <t>Customer is responsible for managing customer-managed keys: (a) creation with appropriate key type and size, (b) rotation policy enabled, (c) Key Vault access policies / RBAC enforcing least privilege, (d) diagnostic logging of all key operations, and (e) soft-delete and purge protection prior to permanent removal.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1403,27 +1403,27 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>SI-2</t>
+          <t>SC-13</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Flaw Remediation</t>
+          <t>Cryptographic Protection</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Inherited</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Microsoft identifies and remediates flaws in Azure-managed services per the Microsoft Vulnerability Management program and publishes service security advisories.</t>
+          <t>Microsoft provides FIPS 140-2 validated cryptographic modules within Azure Government via Key Vault, Managed HSM, and FIPS-validated service endpoints; the customer workload consumes only these validated modules and implements no independent cryptography.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for remediating flaws in customer-managed components: (a) guest OS and application patching via Azure Update Manager, (b) Defender for Cloud recommendations remediation per SLA, (c) Critical CVEs within 30 days and High within 90 days of disclosure, (d) CISA Known Exploited Vulnerabilities entries within the BOD 22-01 mandated window, and (e) a documented exception process.</t>
+          <t>Customer fully inherits the FIPS 140-2 validated cryptographic modules provided by Azure Government. The customer SSP references the Azure Government FedRAMP High SSP as the authoritative source; no customer-side cryptographic implementation is required for this control.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>SI-3</t>
+          <t>SI-2</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Malicious Code Protection</t>
+          <t>Flaw Remediation</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Microsoft protects Azure-managed infrastructure against malicious code via internal endpoint protection and continuous SOC monitoring.</t>
+          <t>Microsoft identifies and remediates flaws in Azure-managed services per the Microsoft Vulnerability Management program and publishes service security advisories.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for deploying malicious code protection on customer workloads: Microsoft Defender for Servers or vendor EDR on VMs, Defender for Containers on AKS, signature/engine updates within 24 hours of release, and remediation of detections per IR-4.</t>
+          <t>Customer is responsible for remediating flaws in customer-managed components: (a) guest OS and application patching via Azure Update Manager, (b) Defender for Cloud recommendations remediation per SLA, (c) Critical CVEs within 30 days and High within 90 days of disclosure, (d) CISA Known Exploited Vulnerabilities entries within the BOD 22-01 mandated window, and (e) a documented exception process.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>SI-4</t>
+          <t>SI-3</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>System Monitoring</t>
+          <t>Malicious Code Protection</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Microsoft monitors Azure-managed infrastructure via internal SOC tooling with 24x7 coverage and automated alerting.</t>
+          <t>Microsoft protects Azure-managed infrastructure against malicious code via internal endpoint protection and continuous SOC monitoring.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for monitoring customer-deployed workloads via (a) Azure Monitor metrics and alerts, (b) Microsoft Defender for Cloud across all subscriptions, (c) Microsoft Sentinel for SIEM/SOAR correlation, (d) Defender for Cloud vulnerability assessment, and (e) customer SIEM integration where applicable. Alerts triaged per IR-4.</t>
+          <t>Customer is responsible for deploying malicious code protection on customer workloads: Microsoft Defender for Servers or vendor EDR on VMs, Defender for Containers on AKS, signature/engine updates within 24 hours of release, and remediation of detections per IR-4.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>MP-6</t>
+          <t>SI-4</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Media Sanitization</t>
+          <t>System Monitoring</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Microsoft sanitizes decommissioned physical storage media per NIST SP 800-88 Rev. 1 with documented certificates of destruction.</t>
+          <t>Microsoft monitors Azure-managed infrastructure via internal SOC tooling with 24x7 coverage and automated alerting.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for sanitizing customer-managed data: disk deletion (customer-managed key deletion = cryptographic erasure), purging versioned storage including soft-deleted blobs, database deletion, and scheduled purge of customer-managed Key Vault keys that encrypted retired data.</t>
+          <t>Customer is responsible for monitoring customer-deployed workloads via (a) Azure Monitor metrics and alerts, (b) Microsoft Defender for Cloud across all subscriptions, (c) Microsoft Sentinel for SIEM/SOAR correlation, (d) Defender for Cloud vulnerability assessment, and (e) customer SIEM integration where applicable. Alerts triaged per IR-4.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1531,27 +1531,27 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>AT-1</t>
+          <t>MP-6</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Awareness and Training Policy and Procedures</t>
+          <t>Media Sanitization</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the Azure service boundary. Customer maintains the awareness and training policy independently.</t>
+          <t>Microsoft sanitizes decommissioned physical storage media per NIST SP 800-88 Rev. 1 with documented certificates of destruction.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing, documenting, disseminating, and annually reviewing the customer security awareness and training policy applicable to all personnel with access to customer information systems.</t>
+          <t>Customer is responsible for sanitizing customer-managed data: disk deletion (customer-managed key deletion = cryptographic erasure), purging versioned storage including soft-deleted blobs, database deletion, and scheduled purge of customer-managed Key Vault keys that encrypted retired data.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>AT-2</t>
+          <t>AT-1</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Literacy Training and Awareness</t>
+          <t>Awareness and Training Policy and Procedures</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the Azure service boundary.</t>
+          <t>Not applicable to the Azure service boundary. Customer maintains the awareness and training policy independently.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for providing security literacy training and awareness to all customer information system users on initial access, annually thereafter, and following significant environmental change, including role-based content.</t>
+          <t>Customer is responsible for developing, documenting, disseminating, and annually reviewing the customer security awareness and training policy applicable to all personnel with access to customer information systems.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>AT-3</t>
+          <t>AT-2</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Role-Based Training</t>
+          <t>Literacy Training and Awareness</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for providing role-based security training to personnel with significant security responsibilities (cloud administrators, security engineers, developers with production access) prior to access authorization and annually thereafter.</t>
+          <t>Customer is responsible for providing security literacy training and awareness to all customer information system users on initial access, annually thereafter, and following significant environmental change, including role-based content.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -1627,12 +1627,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>PL-2</t>
+          <t>AT-3</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>System Security and Privacy Plans</t>
+          <t>Role-Based Training</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1642,12 +1642,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the Azure service boundary. Customer maintains the System Security Plan independently.</t>
+          <t>Not applicable to the Azure service boundary.</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing and maintaining the customer System Security Plan covering customer-deployed workloads, customer responsibilities, and the explicit inheritance and shared responsibility relationships with Microsoft per this CRM.</t>
+          <t>Customer is responsible for providing role-based security training to personnel with significant security responsibilities (cloud administrators, security engineers, developers with production access) prior to access authorization and annually thereafter.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>PM-9</t>
+          <t>PL-2</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Risk Management Strategy</t>
+          <t>System Security and Privacy Plans</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the Azure service boundary.</t>
+          <t>Not applicable to the Azure service boundary. Customer maintains the System Security Plan independently.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing and implementing the customer Risk Management Strategy, including risk tolerance for customer-managed workloads in Azure Government and risk framing for the inherited and shared portions of the shared responsibility model.</t>
+          <t>Customer is responsible for developing and maintaining the customer System Security Plan covering customer-deployed workloads, customer responsibilities, and the explicit inheritance and shared responsibility relationships with Microsoft per this CRM.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>RA-3</t>
+          <t>PM-9</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Risk Assessment</t>
+          <t>Risk Management Strategy</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for conducting risk assessments of customer-deployed systems at least annually and following significant change, incorporating the Azure shared responsibility model and the customer-specific threat landscape.</t>
+          <t>Customer is responsible for developing and implementing the customer Risk Management Strategy, including risk tolerance for customer-managed workloads in Azure Government and risk framing for the inherited and shared portions of the shared responsibility model.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>RA-5</t>
+          <t>RA-3</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Vulnerability Monitoring and Scanning</t>
+          <t>Risk Assessment</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the Azure service boundary. Microsoft scans Azure-managed infrastructure independently.</t>
+          <t>Not applicable to the Azure service boundary.</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for vulnerability scanning of customer-deployed workloads via Microsoft Defender for Cloud vulnerability assessment, customer third-party scanners (Tenable Nessus, Qualys), and remediating findings per customer SLAs aligned to SI-2.</t>
+          <t>Customer is responsible for conducting risk assessments of customer-deployed systems at least annually and following significant change, incorporating the Azure shared responsibility model and the customer-specific threat landscape.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -1755,62 +1755,94 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>PE-10</t>
+          <t>RA-5</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Emergency Shutoff</t>
+          <t>Vulnerability Monitoring and Scanning</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the Azure Government customer service offering. Datacenter emergency power shutoff is a Microsoft-internal facility control not exposed to customer interaction.</t>
+          <t>Not applicable to the Azure service boundary. Microsoft scans Azure-managed infrastructure independently.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to customer. Customer has no role in datacenter emergency shutoff procedures and no requirement to implement an equivalent compensating control.</t>
+          <t>Customer is responsible for vulnerability scanning of customer-deployed workloads via Microsoft Defender for Cloud vulnerability assessment, customer third-party scanners (Tenable Nessus, Qualys), and remediating findings per customer SLAs aligned to SI-2.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Not Implemented</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>PE-10</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Emergency Shutoff</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable to the Azure Government customer service offering. Datacenter emergency power shutoff is a Microsoft-internal facility control not exposed to customer interaction.</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable to customer. Customer has no role in datacenter emergency shutoff procedures and no requirement to implement an equivalent compensating control.</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Not Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
           <t>PE-11</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Emergency Power</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Not applicable to the Azure Government customer service offering. Microsoft provides datacenter emergency power (UPS, generators, fuel reserves) as an internal infrastructure control.</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Not applicable to customer. Azure datacenter emergency power is fully internal to Microsoft facilities; customer has no implementation or compensating-control responsibility.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Not Implemented</t>
         </is>

--- a/demo/crm/Azure_Government_FedRAMP_High_CRM.xlsx
+++ b/demo/crm/Azure_Government_FedRAMP_High_CRM.xlsx
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Inherited</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Microsoft sanitizes decommissioned physical storage media per NIST SP 800-88 Rev. 1 with documented certificates of destruction.</t>
+          <t>Microsoft sanitizes decommissioned physical storage media per NIST SP 800-88 Rev. 1 with documented certificates of destruction, and performs cryptographic erasure of the customer-managed media plane on the Azure Government enclave.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for sanitizing customer-managed data: disk deletion (customer-managed key deletion = cryptographic erasure), purging versioned storage including soft-deleted blobs, database deletion, and scheduled purge of customer-managed Key Vault keys that encrypted retired data.</t>
+          <t>Customer fully inherits Azure Government media sanitization for this system; no customer-side media-sanitization implementation is required on this enclave.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">

--- a/demo/crm/Azure_Government_FedRAMP_High_CRM.xlsx
+++ b/demo/crm/Azure_Government_FedRAMP_High_CRM.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -603,12 +603,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>PE-6</t>
+          <t>PE-8</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Monitoring Physical Access</t>
+          <t>Visitor Access Records</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -618,12 +618,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Microsoft monitors datacenter physical access via CCTV with 90-day minimum retention, intrusion-detection sensors, and continuous review by the Microsoft datacenter security operations team with automated alerting on anomalous access.</t>
+          <t>Microsoft maintains visitor access records for all Azure Government datacenter facilities, logging visitor identity, escort, purpose, and entry/exit times, retained and reviewed per Microsoft facility-security procedures.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Customer fully inherits Azure physical access monitoring. Customer may review the Azure SOC 2 Type II and FedRAMP High audit reports via the Service Trust Portal for assurance evidence.</t>
+          <t>Customer fully inherits Azure datacenter visitor access records. Customer personnel are not granted physical access to Azure Government datacenters, so there is no customer-side cloud visitor log. The customer remains responsible for visitor access records at any customer-operated on-premises facility hosting the system's flex footprint.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -635,12 +635,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>PE-13</t>
+          <t>PE-6</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Fire Protection</t>
+          <t>Monitoring Physical Access</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -650,12 +650,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Azure datacenters deploy very-early smoke detection, pre-action dry-pipe suppression, handheld extinguishers per NFPA 10, and conduct quarterly inspection with annual recertification of suppression equipment.</t>
+          <t>Microsoft monitors datacenter physical access via CCTV with 90-day minimum retention, intrusion-detection sensors, and continuous review by the Microsoft datacenter security operations team with automated alerting on anomalous access.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Customer fully inherits Azure datacenter fire protection. Customer data is protected against facility-level events through customer-implemented availability-zone / geo-redundant replication per CP-9.</t>
+          <t>Customer fully inherits Azure physical access monitoring. Customer may review the Azure SOC 2 Type II and FedRAMP High audit reports via the Service Trust Portal for assurance evidence.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -667,12 +667,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>PE-14</t>
+          <t>PE-13</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Environmental Controls</t>
+          <t>Fire Protection</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -682,12 +682,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Microsoft maintains datacenter temperature and humidity within ASHRAE ranges via N+1 redundant cooling with continuous monitoring and automated failover.</t>
+          <t>Azure datacenters deploy very-early smoke detection, pre-action dry-pipe suppression, handheld extinguishers per NFPA 10, and conduct quarterly inspection with annual recertification of suppression equipment.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Customer fully inherits Azure datacenter environmental controls. No customer-side implementation responsibility.</t>
+          <t>Customer fully inherits Azure datacenter fire protection. Customer data is protected against facility-level events through customer-implemented availability-zone / geo-redundant replication per CP-9.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -699,27 +699,27 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>PE-4</t>
+          <t>PE-14</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Access Control for Transmission</t>
+          <t>Environmental Controls</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Inherited</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Microsoft controls physical access to all information system transmission and distribution lines within Azure datacenter facilities, including intra-facility fiber, copper, and power distribution.</t>
+          <t>Microsoft maintains datacenter temperature and humidity within ASHRAE ranges via N+1 redundant cooling with continuous monitoring and automated failover.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Provider-owned. Customer has no role in physical transmission-line access control within Azure datacenters and no compensating-control responsibility.</t>
+          <t>Customer fully inherits Azure datacenter environmental controls. No customer-side implementation responsibility.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -731,12 +731,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>PE-5</t>
+          <t>PE-4</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Access Control for Output Devices</t>
+          <t>Access Control for Transmission</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Microsoft controls physical access to output devices within Azure datacenter facilities. No physical output devices are provided to customers; all customer interaction occurs via authenticated remote APIs and the Azure portal.</t>
+          <t>Microsoft controls physical access to all information system transmission and distribution lines within Azure datacenter facilities, including intra-facility fiber, copper, and power distribution.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Provider-owned. Customer does not maintain physical output devices in Azure facilities. Not applicable to customer.</t>
+          <t>Provider-owned. Customer has no role in physical transmission-line access control within Azure datacenters and no compensating-control responsibility.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -763,27 +763,27 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AC-1</t>
+          <t>PE-5</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Access Control Policy and Procedures</t>
+          <t>Access Control for Output Devices</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Microsoft maintains internal access control policy for Microsoft personnel and Azure-managed infrastructure, reviewed annually.</t>
+          <t>Microsoft controls physical access to output devices within Azure datacenter facilities. No physical output devices are provided to customers; all customer interaction occurs via authenticated remote APIs and the Azure portal.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing, documenting, disseminating, and annually reviewing the customer-side access control policy governing customer use of Azure services and customer-deployed workloads. Customer SSP must document the AC-1 policy and its mission alignment.</t>
+          <t>Provider-owned. Customer does not maintain physical output devices in Azure facilities. Not applicable to customer.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -795,12 +795,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AC-2</t>
+          <t>AC-1</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Account Management</t>
+          <t>Access Control Policy and Procedures</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -810,12 +810,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Microsoft manages Microsoft-internal personnel accounts per Microsoft Personnel Security policy and provides Microsoft Entra ID, Privileged Identity Management (PIM), and managed identities as account-management primitives for customer use.</t>
+          <t>Microsoft maintains internal access control policy for Microsoft personnel and Azure-managed infrastructure, reviewed annually.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for the full lifecycle of customer Entra ID users, groups, service principals, and managed identities, including (a) provisioning per documented request/approval workflow, (b) deprovisioning within 24 hours of role change or separation, (c) quarterly access reviews via Entra ID Access Reviews, (d) automated disabling of accounts inactive &gt;=90 days, and (e) MFA enforcement on all Global Administrator accounts.</t>
+          <t>Customer is responsible for developing, documenting, disseminating, and annually reviewing the customer-side access control policy governing customer use of Azure services and customer-deployed workloads. Customer SSP must document the AC-1 policy and its mission alignment.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -827,12 +827,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AC-3</t>
+          <t>AC-2</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Access Enforcement</t>
+          <t>Account Management</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -842,12 +842,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Microsoft enforces access at the Azure Resource Manager control-plane layer; requests not authorized by an applicable Azure RBAC role assignment or Azure Policy are denied.</t>
+          <t>Microsoft manages Microsoft-internal personnel accounts per Microsoft Personnel Security policy and provides Microsoft Entra ID, Privileged Identity Management (PIM), and managed identities as account-management primitives for customer use.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for authoring and maintaining Azure RBAC role assignments, custom roles, Azure Policy assignments, and Conditional Access policies that enforce least-privilege access to customer-owned resources, and for validating effective access prior to deployment.</t>
+          <t>Customer is responsible for the full lifecycle of customer Entra ID users, groups, service principals, and managed identities, including (a) provisioning per documented request/approval workflow, (b) deprovisioning within 24 hours of role change or separation, (c) quarterly access reviews via Entra ID Access Reviews, (d) automated disabling of accounts inactive &gt;=90 days, and (e) MFA enforcement on all Global Administrator accounts.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AC-6</t>
+          <t>AC-3</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Least Privilege</t>
+          <t>Access Enforcement</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Microsoft implements least privilege for Microsoft personnel and Azure service principals via narrowly scoped built-in roles.</t>
+          <t>Microsoft enforces access at the Azure Resource Manager control-plane layer; requests not authorized by an applicable Azure RBAC role assignment or Azure Policy are denied.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for implementing least privilege within customer subscriptions: (a) custom RBAC roles scoped to minimum actions, (b) just-in-time privileged elevation via Entra PIM, (c) periodic review and removal of unused role assignments, and (d) management-group-level Azure Policy to constrain delegated administration.</t>
+          <t>Customer is responsible for authoring and maintaining Azure RBAC role assignments, custom roles, Azure Policy assignments, and Conditional Access policies that enforce least-privilege access to customer-owned resources, and for validating effective access prior to deployment.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -891,12 +891,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AU-2</t>
+          <t>AC-6</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Event Logging</t>
+          <t>Least Privilege</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Microsoft logs all control-plane operations via Azure-internal audit systems and provides Azure Activity Log, Azure Monitor, diagnostic settings, and Microsoft Entra audit logs for customer event capture.</t>
+          <t>Microsoft implements least privilege for Microsoft personnel and Azure service principals via narrowly scoped built-in roles.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for (a) routing Activity Log and resource diagnostic logs to a Log Analytics workspace and immutable storage, (b) enabling data-plane logging on sensitive storage accounts, Key Vaults, and databases, (c) configuring Entra ID sign-in and audit log export, and (d) documenting the customer-defined auditable event list per AU-1.</t>
+          <t>Customer is responsible for implementing least privilege within customer subscriptions: (a) custom RBAC roles scoped to minimum actions, (b) just-in-time privileged elevation via Entra PIM, (c) periodic review and removal of unused role assignments, and (d) management-group-level Azure Policy to constrain delegated administration.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -923,27 +923,27 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>AU-6</t>
+          <t>AU-2</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Audit Record Review, Analysis, and Reporting</t>
+          <t>Event Logging</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Microsoft provides the log sources (Activity Log, Entra audit, Defender for Cloud, Sentinel) but performs no review of customer-tenant audit records on the customer's behalf.</t>
+          <t>Microsoft logs all control-plane operations via Azure-internal audit systems and provides Azure Activity Log, Azure Monitor, diagnostic settings, and Microsoft Entra audit logs for customer event capture.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Customer is solely responsible for reviewing, analyzing, and reporting on customer Activity Logs, Defender for Cloud alerts, Microsoft Sentinel incidents, and application logs on the customer-defined cadence (minimum weekly for non-critical, continuous for critical). The customer operates the Sentinel workspace and escalates reportable findings per IR-6.</t>
+          <t>Customer is responsible for (a) routing Activity Log and resource diagnostic logs to a Log Analytics workspace and immutable storage, (b) enabling data-plane logging on sensitive storage accounts, Key Vaults, and databases, (c) configuring Entra ID sign-in and audit log export, and (d) documenting the customer-defined auditable event list per AU-1.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -955,12 +955,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>AU-9</t>
+          <t>AU-6</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Protection of Audit Information</t>
+          <t>Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -970,12 +970,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Microsoft provides immutable storage primitives (Azure Blob immutable time-based retention / legal hold, Key Vault, Azure RBAC) but does not configure them on customer storage accounts.</t>
+          <t>Microsoft provides the log sources (Activity Log, Entra audit, Defender for Cloud, Sentinel) but performs no review of customer-tenant audit records on the customer's behalf.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for protecting customer audit information: enabling immutable (WORM) time-based retention on the audit-log storage account, restricting access via least-privilege Azure RBAC, and enabling customer-managed-key encryption so audit records cannot be modified or deleted.</t>
+          <t>Customer is solely responsible for reviewing, analyzing, and reporting on customer Activity Logs, Defender for Cloud alerts, Microsoft Sentinel incidents, and application logs on the customer-defined cadence (minimum weekly for non-critical, continuous for critical). The customer operates the Sentinel workspace and escalates reportable findings per IR-6.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -987,27 +987,27 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>AU-12</t>
+          <t>AU-9</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Audit Record Generation</t>
+          <t>Protection of Audit Information</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Microsoft generates audit records for all Azure control-plane and Azure-internal service operations per Microsoft audit policy.</t>
+          <t>Microsoft provides immutable storage primitives (Azure Blob immutable time-based retention / legal hold, Key Vault, Azure RBAC) but does not configure them on customer storage accounts.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for enabling audit record generation on all customer-deployed systems: VM guest OS auditd / Windows Event Log via Azure Monitor Agent, Azure SQL audit, container runtime logs, and application logs, forwarded to a tamper-resistant Log Analytics workspace or immutable storage.</t>
+          <t>Customer is responsible for protecting customer audit information: enabling immutable (WORM) time-based retention on the audit-log storage account, restricting access via least-privilege Azure RBAC, and enabling customer-managed-key encryption so audit records cannot be modified or deleted.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1019,12 +1019,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>CM-2</t>
+          <t>AU-12</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Baseline Configuration</t>
+          <t>Audit Record Generation</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Microsoft maintains baseline configurations for all Azure-managed infrastructure and services per Microsoft configuration management policy.</t>
+          <t>Microsoft generates audit records for all Azure control-plane and Azure-internal service operations per Microsoft audit policy.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing and maintaining baseline configurations for customer-managed VM images, container images, and Infrastructure-as-Code templates (ARM, Bicep, Terraform). Baselines reviewed at least annually and after significant change; drift detected via Azure Policy guest configuration / Machine Configuration.</t>
+          <t>Customer is responsible for enabling audit record generation on all customer-deployed systems: VM guest OS auditd / Windows Event Log via Azure Monitor Agent, Azure SQL audit, container runtime logs, and application logs, forwarded to a tamper-resistant Log Analytics workspace or immutable storage.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1051,12 +1051,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>CM-6</t>
+          <t>CM-2</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Configuration Settings</t>
+          <t>Baseline Configuration</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Microsoft configures Azure-managed services per Microsoft security baselines aligned to the Microsoft cloud security benchmark.</t>
+          <t>Microsoft maintains baseline configurations for all Azure-managed infrastructure and services per Microsoft configuration management policy.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for (a) hardening customer-managed OS images per DISA STIG or CIS Benchmarks, (b) continuously enforcing configuration via Azure Policy and Machine Configuration, (c) remediating drift within customer-defined SLAs, and (d) documenting approved deviations with compensating controls.</t>
+          <t>Customer is responsible for developing and maintaining baseline configurations for customer-managed VM images, container images, and Infrastructure-as-Code templates (ARM, Bicep, Terraform). Baselines reviewed at least annually and after significant change; drift detected via Azure Policy guest configuration / Machine Configuration.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>CM-8</t>
+          <t>CM-6</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>System Component Inventory</t>
+          <t>Configuration Settings</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Microsoft maintains a complete inventory of Azure-managed physical and virtual infrastructure supporting the Azure Government offering.</t>
+          <t>Microsoft configures Azure-managed services per Microsoft security baselines aligned to the Microsoft cloud security benchmark.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for maintaining an accurate inventory of customer-deployed resources via Azure Resource Graph, Azure Resource tags, and Defender for Cloud asset inventory, reconciled at least monthly.</t>
+          <t>Customer is responsible for (a) hardening customer-managed OS images per DISA STIG or CIS Benchmarks, (b) continuously enforcing configuration via Azure Policy and Machine Configuration, (c) remediating drift within customer-defined SLAs, and (d) documenting approved deviations with compensating controls.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1115,12 +1115,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>CP-9</t>
+          <t>CM-8</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>System Backup</t>
+          <t>System Component Inventory</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Microsoft replicates and backs up Azure-managed control-plane and service data per Microsoft contingency planning policy, with locally and geo-redundant storage durability guarantees.</t>
+          <t>Microsoft maintains a complete inventory of Azure-managed physical and virtual infrastructure supporting the Azure Government offering.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for backing up customer-owned data aligned to customer-defined RPO via Azure Backup vaults, VM and disk snapshots, Azure SQL automated backups with geo-restore, and geo-redundant storage replication. Backup integrity tested per CP-4.</t>
+          <t>Customer is responsible for maintaining an accurate inventory of customer-deployed resources via Azure Resource Graph, Azure Resource tags, and Defender for Cloud asset inventory, reconciled at least monthly.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1147,12 +1147,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>IA-2</t>
+          <t>CP-9</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Identification and Authentication (Organizational Users)</t>
+          <t>System Backup</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Microsoft authenticates Microsoft personnel via internal MFA and PIV-equivalent credentials and provides Microsoft Entra ID with Conditional Access and FIDO2 / certificate-based authentication for customer use.</t>
+          <t>Microsoft replicates and backs up Azure-managed control-plane and service data per Microsoft contingency planning policy, with locally and geo-redundant storage durability guarantees.</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for (a) enforcing MFA on all customer Entra ID users via Conditional Access, with phishing-resistant MFA for privileged roles, (b) federating with the customer enterprise IdP where applicable, (c) enforcing FIPS 140-validated authenticators for government-user access, and (d) blocking legacy authentication protocols.</t>
+          <t>Customer is responsible for backing up customer-owned data aligned to customer-defined RPO via Azure Backup vaults, VM and disk snapshots, Azure SQL automated backups with geo-restore, and geo-redundant storage replication. Backup integrity tested per CP-4.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1179,12 +1179,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>IA-5</t>
+          <t>IA-2</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Authenticator Management</t>
+          <t>Identification and Authentication (Organizational Users)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Microsoft manages authenticators for Microsoft personnel per Microsoft Personnel Security policy including issuance, rotation, and revocation.</t>
+          <t>Microsoft authenticates Microsoft personnel via internal MFA and PIV-equivalent credentials and provides Microsoft Entra ID with Conditional Access and FIDO2 / certificate-based authentication for customer use.</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for managing customer-side authenticators: (a) Entra ID password protection and ban-list policy, (b) service-principal secret and certificate rotation, (c) MFA device lifecycle including loss reporting and re-issuance, and (d) Azure Key Vault rotation policies for application secrets and certificates.</t>
+          <t>Customer is responsible for (a) enforcing MFA on all customer Entra ID users via Conditional Access, with phishing-resistant MFA for privileged roles, (b) federating with the customer enterprise IdP where applicable, (c) enforcing FIPS 140-validated authenticators for government-user access, and (d) blocking legacy authentication protocols.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1211,12 +1211,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>IR-4</t>
+          <t>IA-5</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Incident Handling</t>
+          <t>Authenticator Management</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Microsoft handles incidents affecting Azure-managed infrastructure per the Microsoft Security Response process and notifies affected customers per the Microsoft Online Services Terms.</t>
+          <t>Microsoft manages authenticators for Microsoft personnel per Microsoft Personnel Security policy including issuance, rotation, and revocation.</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for incident handling within the customer environment: detection via Defender for Cloud and Microsoft Sentinel, triage per customer playbooks, containment via Conditional Access revocation and NSG isolation, eradication and recovery per the customer IR plan, and breach notification per regulatory obligations.</t>
+          <t>Customer is responsible for managing customer-side authenticators: (a) Entra ID password protection and ban-list policy, (b) service-principal secret and certificate rotation, (c) MFA device lifecycle including loss reporting and re-issuance, and (d) Azure Key Vault rotation policies for application secrets and certificates.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1243,12 +1243,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>IR-6</t>
+          <t>IR-4</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Incident Reporting</t>
+          <t>Incident Handling</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Microsoft reports incidents affecting Azure-managed infrastructure to affected customers and to the FedRAMP PMO per Microsoft incident reporting procedures.</t>
+          <t>Microsoft handles incidents affecting Azure-managed infrastructure per the Microsoft Security Response process and notifies affected customers per the Microsoft Online Services Terms.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for reporting customer-environment incidents to customer authorities, to US-CERT per FISMA timeframes, and to the FedRAMP PMO within 1 hour of incident determination for FedRAMP-authorized systems.</t>
+          <t>Customer is responsible for incident handling within the customer environment: detection via Defender for Cloud and Microsoft Sentinel, triage per customer playbooks, containment via Conditional Access revocation and NSG isolation, eradication and recovery per the customer IR plan, and breach notification per regulatory obligations.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1275,12 +1275,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>MA-4</t>
+          <t>IR-6</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Nonlocal Maintenance</t>
+          <t>Incident Reporting</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Microsoft authorizes, monitors, and audits all nonlocal maintenance on Azure-managed infrastructure via approved internal access paths with MFA and full session recording.</t>
+          <t>Microsoft reports incidents affecting Azure-managed infrastructure to affected customers and to the FedRAMP PMO per Microsoft incident reporting procedures.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for nonlocal maintenance of customer-managed resources: administrative access via Azure Bastion (no direct public SSH/RDP), MFA on all administrative sessions, session logging to immutable storage, and FIPS-validated transport for administrative connections.</t>
+          <t>Customer is responsible for reporting customer-environment incidents to customer authorities, to US-CERT per FISMA timeframes, and to the FedRAMP PMO within 1 hour of incident determination for FedRAMP-authorized systems.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1307,12 +1307,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>SC-7</t>
+          <t>MA-4</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Boundary Protection</t>
+          <t>Nonlocal Maintenance</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Microsoft provides Virtual Network, Network Security Groups, Azure Firewall, DDoS Protection, Application Gateway WAF, and Private Link as boundary-protection primitives, and protects the Azure service boundary at the control-plane layer.</t>
+          <t>Microsoft authorizes, monitors, and audits all nonlocal maintenance on Azure-managed infrastructure via approved internal access paths with MFA and full session recording.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for designing the customer virtual-network boundary: (a) subnet segmentation, (b) NSG rules enforcing least-privilege flows, (c) Azure Firewall for centralized egress filtering, (d) WAF on internet-facing Application Gateways and Front Door, (e) Private Endpoints for PaaS services, and (f) enforcement of the customer-defined trust-zone boundary.</t>
+          <t>Customer is responsible for nonlocal maintenance of customer-managed resources: administrative access via Azure Bastion (no direct public SSH/RDP), MFA on all administrative sessions, session logging to immutable storage, and FIPS-validated transport for administrative connections.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1339,12 +1339,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>SC-8</t>
+          <t>SC-7</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Transmission Confidentiality and Integrity</t>
+          <t>Boundary Protection</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Microsoft encrypts data in transit between Azure services and across regions using TLS 1.2+ with FIPS-validated cipher suites and physically protects inter-datacenter fiber.</t>
+          <t>Microsoft provides Virtual Network, Network Security Groups, Azure Firewall, DDoS Protection, Application Gateway WAF, and Private Link as boundary-protection primitives, and protects the Azure service boundary at the control-plane layer.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for (a) enforcing TLS 1.2+ on all customer-facing endpoints, (b) configuring only approved FIPS-validated cipher suites, (c) enforcing HTTPS-only access, (d) application-layer TLS for service-to-service traffic, and (e) using Azure Government FIPS endpoints for FISMA-regulated systems.</t>
+          <t>Customer is responsible for designing the customer virtual-network boundary: (a) subnet segmentation, (b) NSG rules enforcing least-privilege flows, (c) Azure Firewall for centralized egress filtering, (d) WAF on internet-facing Application Gateways and Front Door, (e) Private Endpoints for PaaS services, and (f) enforcement of the customer-defined trust-zone boundary.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>SC-12</t>
+          <t>SC-8</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Cryptographic Key Establishment and Management</t>
+          <t>Transmission Confidentiality and Integrity</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Microsoft manages keys for Microsoft-managed encryption and provides Azure Key Vault (FIPS 140-2 Level 2 validated HSMs) and Azure Key Vault Managed HSM (FIPS 140-2 Level 3) for customer key management.</t>
+          <t>Microsoft encrypts data in transit between Azure services and across regions using TLS 1.2+ with FIPS-validated cipher suites and physically protects inter-datacenter fiber.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for managing customer-managed keys: (a) creation with appropriate key type and size, (b) rotation policy enabled, (c) Key Vault access policies / RBAC enforcing least privilege, (d) diagnostic logging of all key operations, and (e) soft-delete and purge protection prior to permanent removal.</t>
+          <t>Customer is responsible for (a) enforcing TLS 1.2+ on all customer-facing endpoints, (b) configuring only approved FIPS-validated cipher suites, (c) enforcing HTTPS-only access, (d) application-layer TLS for service-to-service traffic, and (e) using Azure Government FIPS endpoints for FISMA-regulated systems.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1403,27 +1403,27 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>SC-13</t>
+          <t>SC-12</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Cryptographic Protection</t>
+          <t>Cryptographic Key Establishment and Management</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Inherited</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Microsoft provides FIPS 140-2 validated cryptographic modules within Azure Government via Key Vault, Managed HSM, and FIPS-validated service endpoints; the customer workload consumes only these validated modules and implements no independent cryptography.</t>
+          <t>Microsoft manages keys for Microsoft-managed encryption and provides Azure Key Vault (FIPS 140-2 Level 2 validated HSMs) and Azure Key Vault Managed HSM (FIPS 140-2 Level 3) for customer key management.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Customer fully inherits the FIPS 140-2 validated cryptographic modules provided by Azure Government. The customer SSP references the Azure Government FedRAMP High SSP as the authoritative source; no customer-side cryptographic implementation is required for this control.</t>
+          <t>Customer is responsible for managing customer-managed keys: (a) creation with appropriate key type and size, (b) rotation policy enabled, (c) Key Vault access policies / RBAC enforcing least privilege, (d) diagnostic logging of all key operations, and (e) soft-delete and purge protection prior to permanent removal.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1435,27 +1435,27 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>SI-2</t>
+          <t>SC-13</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Flaw Remediation</t>
+          <t>Cryptographic Protection</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Inherited</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Microsoft identifies and remediates flaws in Azure-managed services per the Microsoft Vulnerability Management program and publishes service security advisories.</t>
+          <t>Microsoft provides FIPS 140-2 validated cryptographic modules within Azure Government via Key Vault, Managed HSM, and FIPS-validated service endpoints; the customer workload consumes only these validated modules and implements no independent cryptography.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for remediating flaws in customer-managed components: (a) guest OS and application patching via Azure Update Manager, (b) Defender for Cloud recommendations remediation per SLA, (c) Critical CVEs within 30 days and High within 90 days of disclosure, (d) CISA Known Exploited Vulnerabilities entries within the BOD 22-01 mandated window, and (e) a documented exception process.</t>
+          <t>Customer fully inherits the FIPS 140-2 validated cryptographic modules provided by Azure Government. The customer SSP references the Azure Government FedRAMP High SSP as the authoritative source; no customer-side cryptographic implementation is required for this control.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>SI-3</t>
+          <t>SI-2</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Malicious Code Protection</t>
+          <t>Flaw Remediation</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Microsoft protects Azure-managed infrastructure against malicious code via internal endpoint protection and continuous SOC monitoring.</t>
+          <t>Microsoft identifies and remediates flaws in Azure-managed services per the Microsoft Vulnerability Management program and publishes service security advisories.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for deploying malicious code protection on customer workloads: Microsoft Defender for Servers or vendor EDR on VMs, Defender for Containers on AKS, signature/engine updates within 24 hours of release, and remediation of detections per IR-4.</t>
+          <t>Customer is responsible for remediating flaws in customer-managed components: (a) guest OS and application patching via Azure Update Manager, (b) Defender for Cloud recommendations remediation per SLA, (c) Critical CVEs within 30 days and High within 90 days of disclosure, (d) CISA Known Exploited Vulnerabilities entries within the BOD 22-01 mandated window, and (e) a documented exception process.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>SI-4</t>
+          <t>SI-3</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>System Monitoring</t>
+          <t>Malicious Code Protection</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Microsoft monitors Azure-managed infrastructure via internal SOC tooling with 24x7 coverage and automated alerting.</t>
+          <t>Microsoft protects Azure-managed infrastructure against malicious code via internal endpoint protection and continuous SOC monitoring.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for monitoring customer-deployed workloads via (a) Azure Monitor metrics and alerts, (b) Microsoft Defender for Cloud across all subscriptions, (c) Microsoft Sentinel for SIEM/SOAR correlation, (d) Defender for Cloud vulnerability assessment, and (e) customer SIEM integration where applicable. Alerts triaged per IR-4.</t>
+          <t>Customer is responsible for deploying malicious code protection on customer workloads: Microsoft Defender for Servers or vendor EDR on VMs, Defender for Containers on AKS, signature/engine updates within 24 hours of release, and remediation of detections per IR-4.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1531,27 +1531,27 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MP-6</t>
+          <t>SI-4</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Media Sanitization</t>
+          <t>System Monitoring</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Inherited</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Microsoft sanitizes decommissioned physical storage media per NIST SP 800-88 Rev. 1 with documented certificates of destruction, and performs cryptographic erasure of the customer-managed media plane on the Azure Government enclave.</t>
+          <t>Microsoft monitors Azure-managed infrastructure via internal SOC tooling with 24x7 coverage and automated alerting.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Customer fully inherits Azure Government media sanitization for this system; no customer-side media-sanitization implementation is required on this enclave.</t>
+          <t>Customer is responsible for monitoring customer-deployed workloads via (a) Azure Monitor metrics and alerts, (b) Microsoft Defender for Cloud across all subscriptions, (c) Microsoft Sentinel for SIEM/SOAR correlation, (d) Defender for Cloud vulnerability assessment, and (e) customer SIEM integration where applicable. Alerts triaged per IR-4.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -1563,27 +1563,27 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>AT-1</t>
+          <t>MP-6</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Awareness and Training Policy and Procedures</t>
+          <t>Media Sanitization</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Inherited</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the Azure service boundary. Customer maintains the awareness and training policy independently.</t>
+          <t>Microsoft sanitizes decommissioned physical storage media per NIST SP 800-88 Rev. 1 with documented certificates of destruction, and performs cryptographic erasure of the customer-managed media plane on the Azure Government enclave.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing, documenting, disseminating, and annually reviewing the customer security awareness and training policy applicable to all personnel with access to customer information systems.</t>
+          <t>Customer fully inherits Azure Government media sanitization for this system; no customer-side media-sanitization implementation is required on this enclave.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>AT-2</t>
+          <t>AT-1</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Literacy Training and Awareness</t>
+          <t>Awareness and Training Policy and Procedures</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the Azure service boundary.</t>
+          <t>Not applicable to the Azure service boundary. Customer maintains the awareness and training policy independently.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for providing security literacy training and awareness to all customer information system users on initial access, annually thereafter, and following significant environmental change, including role-based content.</t>
+          <t>Customer is responsible for developing, documenting, disseminating, and annually reviewing the customer security awareness and training policy applicable to all personnel with access to customer information systems.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -1627,12 +1627,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>AT-3</t>
+          <t>AT-2</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Role-Based Training</t>
+          <t>Literacy Training and Awareness</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for providing role-based security training to personnel with significant security responsibilities (cloud administrators, security engineers, developers with production access) prior to access authorization and annually thereafter.</t>
+          <t>Customer is responsible for providing security literacy training and awareness to all customer information system users on initial access, annually thereafter, and following significant environmental change, including role-based content.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>PL-2</t>
+          <t>AT-3</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>System Security and Privacy Plans</t>
+          <t>Role-Based Training</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the Azure service boundary. Customer maintains the System Security Plan independently.</t>
+          <t>Not applicable to the Azure service boundary.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing and maintaining the customer System Security Plan covering customer-deployed workloads, customer responsibilities, and the explicit inheritance and shared responsibility relationships with Microsoft per this CRM.</t>
+          <t>Customer is responsible for providing role-based security training to personnel with significant security responsibilities (cloud administrators, security engineers, developers with production access) prior to access authorization and annually thereafter.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>PM-9</t>
+          <t>PL-2</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Risk Management Strategy</t>
+          <t>System Security and Privacy Plans</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the Azure service boundary.</t>
+          <t>Not applicable to the Azure service boundary. Customer maintains the System Security Plan independently.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing and implementing the customer Risk Management Strategy, including risk tolerance for customer-managed workloads in Azure Government and risk framing for the inherited and shared portions of the shared responsibility model.</t>
+          <t>Customer is responsible for developing and maintaining the customer System Security Plan covering customer-deployed workloads, customer responsibilities, and the explicit inheritance and shared responsibility relationships with Microsoft per this CRM.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>RA-3</t>
+          <t>PM-9</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Risk Assessment</t>
+          <t>Risk Management Strategy</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for conducting risk assessments of customer-deployed systems at least annually and following significant change, incorporating the Azure shared responsibility model and the customer-specific threat landscape.</t>
+          <t>Customer is responsible for developing and implementing the customer Risk Management Strategy, including risk tolerance for customer-managed workloads in Azure Government and risk framing for the inherited and shared portions of the shared responsibility model.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>RA-5</t>
+          <t>RA-3</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Vulnerability Monitoring and Scanning</t>
+          <t>Risk Assessment</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the Azure service boundary. Microsoft scans Azure-managed infrastructure independently.</t>
+          <t>Not applicable to the Azure service boundary.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for vulnerability scanning of customer-deployed workloads via Microsoft Defender for Cloud vulnerability assessment, customer third-party scanners (Tenable Nessus, Qualys), and remediating findings per customer SLAs aligned to SI-2.</t>
+          <t>Customer is responsible for conducting risk assessments of customer-deployed systems at least annually and following significant change, incorporating the Azure shared responsibility model and the customer-specific threat landscape.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -1787,62 +1787,94 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>PE-10</t>
+          <t>RA-5</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Emergency Shutoff</t>
+          <t>Vulnerability Monitoring and Scanning</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the Azure Government customer service offering. Datacenter emergency power shutoff is a Microsoft-internal facility control not exposed to customer interaction.</t>
+          <t>Not applicable to the Azure service boundary. Microsoft scans Azure-managed infrastructure independently.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to customer. Customer has no role in datacenter emergency shutoff procedures and no requirement to implement an equivalent compensating control.</t>
+          <t>Customer is responsible for vulnerability scanning of customer-deployed workloads via Microsoft Defender for Cloud vulnerability assessment, customer third-party scanners (Tenable Nessus, Qualys), and remediating findings per customer SLAs aligned to SI-2.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Not Implemented</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>PE-10</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Emergency Shutoff</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable to the Azure Government customer service offering. Datacenter emergency power shutoff is a Microsoft-internal facility control not exposed to customer interaction.</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable to customer. Customer has no role in datacenter emergency shutoff procedures and no requirement to implement an equivalent compensating control.</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Not Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
           <t>PE-11</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Emergency Power</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Not applicable to the Azure Government customer service offering. Microsoft provides datacenter emergency power (UPS, generators, fuel reserves) as an internal infrastructure control.</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Not applicable to customer. Azure datacenter emergency power is fully internal to Microsoft facilities; customer has no implementation or compensating-control responsibility.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Not Implemented</t>
         </is>
